--- a/AestheticEMR/vcp/products list.xlsx
+++ b/AestheticEMR/vcp/products list.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+  <workbookPr/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
+    <sheet name="inventory" sheetId="2" r:id="rId2"/>
+    <sheet name="tariffAndInventory" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="23">
   <si>
     <t>Full price</t>
   </si>
@@ -93,8 +90,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Arial"/>
@@ -192,7 +189,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -227,7 +224,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -404,254 +401,672 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="40.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.08203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2">
         <v>20000</v>
       </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2">
         <v>10000</v>
       </c>
-      <c r="C3" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2">
         <v>20000</v>
       </c>
-      <c r="C4" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2">
         <v>5000</v>
       </c>
-      <c r="C5" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2">
         <v>15000</v>
       </c>
-      <c r="C6" s="3">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2">
         <v>35000</v>
       </c>
-      <c r="C7" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="2">
         <v>100000</v>
       </c>
-      <c r="C8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="2">
         <v>22000</v>
       </c>
-      <c r="C9" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="2">
         <v>18000</v>
       </c>
-      <c r="C10" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="2">
         <v>24000</v>
       </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="2">
         <v>24000</v>
       </c>
-      <c r="C12" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="2">
         <v>29000</v>
       </c>
-      <c r="C13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="2">
         <v>32000</v>
       </c>
-      <c r="C14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="2">
         <v>47000</v>
       </c>
-      <c r="C15" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="2">
         <v>38000</v>
       </c>
-      <c r="C16" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="2">
         <v>45000</v>
       </c>
-      <c r="C17" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="3">
         <v>33000</v>
       </c>
-      <c r="C18" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19" s="3">
         <v>105000</v>
       </c>
-      <c r="C19" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20" s="3">
         <v>112000</v>
       </c>
-      <c r="C20" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="3">
         <v>10000</v>
-      </c>
-      <c r="C21" s="3">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2">
+        <v>20000</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2">
+        <v>10000</v>
+      </c>
+      <c r="C3" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2">
+        <v>20000</v>
+      </c>
+      <c r="C4" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
+        <v>5000</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2">
+        <v>15000</v>
+      </c>
+      <c r="C6" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2">
+        <v>35000</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2">
+        <v>100000</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2">
+        <v>22000</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2">
+        <v>18000</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2">
+        <v>24000</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2">
+        <v>24000</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2">
+        <v>29000</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="2">
+        <v>32000</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>47000</v>
+      </c>
+      <c r="C15" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>38000</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <v>45000</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="3">
+        <v>33000</v>
+      </c>
+      <c r="C18" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="3">
+        <v>105000</v>
+      </c>
+      <c r="C19" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="3">
+        <v>112000</v>
+      </c>
+      <c r="C20" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="3">
+        <v>10000</v>
+      </c>
+      <c r="C21" s="3">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2">
+        <v>20000</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2">
+        <v>10000</v>
+      </c>
+      <c r="C3" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2">
+        <v>20000</v>
+      </c>
+      <c r="C4" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
+        <v>5000</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2">
+        <v>15000</v>
+      </c>
+      <c r="C6" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2">
+        <v>35000</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2">
+        <v>100000</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2">
+        <v>22000</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2">
+        <v>18000</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2">
+        <v>24000</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2">
+        <v>24000</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2">
+        <v>29000</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="2">
+        <v>32000</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>47000</v>
+      </c>
+      <c r="C15" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>38000</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <v>45000</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="3">
+        <v>33000</v>
+      </c>
+      <c r="C18" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="3">
+        <v>105000</v>
+      </c>
+      <c r="C19" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="3">
+        <v>112000</v>
+      </c>
+      <c r="C20" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="3">
+        <v>10000</v>
+      </c>
+      <c r="C21" s="3">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AestheticEMR/vcp/products list.xlsx
+++ b/AestheticEMR/vcp/products list.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -401,7 +401,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -593,6 +593,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
